--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="100">
   <si>
     <t>#</t>
   </si>
@@ -384,6 +384,30 @@
     <t>承担额外百分比伤害</t>
   </si>
   <si>
+    <t>绝对免伤</t>
+  </si>
+  <si>
+    <t>二次闪避</t>
+  </si>
+  <si>
+    <t>攻击倍率</t>
+  </si>
+  <si>
+    <t>防御倍率</t>
+  </si>
+  <si>
+    <t>生命倍率</t>
+  </si>
+  <si>
+    <t>物攻倍率</t>
+  </si>
+  <si>
+    <t>魔法倍率</t>
+  </si>
+  <si>
+    <t>道术倍率</t>
+  </si>
+  <si>
     <t>吸血</t>
   </si>
   <si>
@@ -454,6 +478,15 @@
   </si>
   <si>
     <t>控制-晕眩</t>
+  </si>
+  <si>
+    <t>麻痹</t>
+  </si>
+  <si>
+    <t>麻痹{2}秒</t>
+  </si>
+  <si>
+    <t>控制-麻痹</t>
   </si>
   <si>
     <t>免疫控制</t>
@@ -1439,7 +1472,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:O37"/>
+  <dimension ref="C1:O52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -2212,484 +2245,1070 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C23" s="1">
+    <row r="22" customHeight="1" spans="3:13">
+      <c r="C22" s="2">
+        <v>18</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="2">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H22" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I22" s="2">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2">
+        <v>37</v>
+      </c>
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C23" s="2">
+        <v>19</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H23" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I23" s="2">
+        <v>1</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0</v>
+      </c>
+      <c r="K23" s="2">
+        <v>39</v>
+      </c>
+      <c r="L23" s="2">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+    </row>
+    <row r="24" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C24" s="2">
+        <v>20</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E24" s="2">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H24" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I24" s="2">
+        <v>1</v>
+      </c>
+      <c r="J24" s="2">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2">
+        <v>2001</v>
+      </c>
+      <c r="L24" s="2">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+    </row>
+    <row r="25" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C25" s="2">
+        <v>21</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="2">
+        <v>1</v>
+      </c>
+      <c r="F25" s="2">
+        <v>1</v>
+      </c>
+      <c r="G25" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H25" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I25" s="2">
+        <v>1</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2">
+        <v>2002</v>
+      </c>
+      <c r="L25" s="2">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+    </row>
+    <row r="26" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C26" s="2">
+        <v>22</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="2">
+        <v>1</v>
+      </c>
+      <c r="F26" s="2">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H26" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I26" s="2">
+        <v>1</v>
+      </c>
+      <c r="J26" s="2">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2">
+        <v>2003</v>
+      </c>
+      <c r="L26" s="2">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C27" s="2">
+        <v>23</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" s="2">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H27" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I27" s="2">
+        <v>1</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2">
+        <v>2004</v>
+      </c>
+      <c r="L27" s="2">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C28" s="2">
+        <v>24</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1</v>
+      </c>
+      <c r="F28" s="2">
+        <v>1</v>
+      </c>
+      <c r="G28" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H28" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I28" s="2">
+        <v>1</v>
+      </c>
+      <c r="J28" s="2">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2">
+        <v>2005</v>
+      </c>
+      <c r="L28" s="2">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+    </row>
+    <row r="29" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C29" s="2">
+        <v>25</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1</v>
+      </c>
+      <c r="G29" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H29" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I29" s="2">
+        <v>1</v>
+      </c>
+      <c r="J29" s="2">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2">
+        <v>2006</v>
+      </c>
+      <c r="L29" s="2">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2">
+        <v>0</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+    </row>
+    <row r="30" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C30" s="2">
+        <v>26</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="2">
+        <v>1</v>
+      </c>
+      <c r="F30" s="2">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H30" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I30" s="2">
+        <v>4</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2">
+        <v>2001</v>
+      </c>
+      <c r="L30" s="2">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+    </row>
+    <row r="31" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C31" s="2">
+        <v>27</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" s="2">
+        <v>1</v>
+      </c>
+      <c r="F31" s="2">
+        <v>1</v>
+      </c>
+      <c r="G31" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H31" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I31" s="2">
+        <v>4</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2">
+        <v>2002</v>
+      </c>
+      <c r="L31" s="2">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+    </row>
+    <row r="32" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C32" s="2">
+        <v>28</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E32" s="2">
+        <v>1</v>
+      </c>
+      <c r="F32" s="2">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H32" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I32" s="2">
+        <v>4</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2">
+        <v>2003</v>
+      </c>
+      <c r="L32" s="2">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2">
+        <v>0</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+    </row>
+    <row r="33" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C33" s="2">
+        <v>29</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E33" s="2">
+        <v>1</v>
+      </c>
+      <c r="F33" s="2">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H33" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I33" s="2">
+        <v>4</v>
+      </c>
+      <c r="J33" s="2">
+        <v>0</v>
+      </c>
+      <c r="K33" s="2">
+        <v>2004</v>
+      </c>
+      <c r="L33" s="2">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2">
+        <v>0</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+    </row>
+    <row r="34" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C34" s="2">
+        <v>30</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H34" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I34" s="2">
+        <v>4</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0</v>
+      </c>
+      <c r="K34" s="2">
+        <v>2005</v>
+      </c>
+      <c r="L34" s="2">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2">
+        <v>0</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+    </row>
+    <row r="35" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C35" s="2">
+        <v>31</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E35" s="2">
+        <v>1</v>
+      </c>
+      <c r="F35" s="2">
+        <v>1</v>
+      </c>
+      <c r="G35" s="2">
+        <v>-2</v>
+      </c>
+      <c r="H35" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I35" s="2">
+        <v>4</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0</v>
+      </c>
+      <c r="K35" s="2">
+        <v>2006</v>
+      </c>
+      <c r="L35" s="2">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2">
+        <v>0</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+    </row>
+    <row r="36" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C37" s="1">
         <v>101</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="1">
+      <c r="D37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E37" s="1">
         <v>2</v>
       </c>
-      <c r="F23" s="1">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H23" s="1">
-        <v>1</v>
-      </c>
-      <c r="I23" s="1">
-        <v>1</v>
-      </c>
-      <c r="J23" s="1">
-        <v>0</v>
-      </c>
-      <c r="K23" s="1">
-        <v>0</v>
-      </c>
-      <c r="L23" s="1">
-        <v>0</v>
-      </c>
-      <c r="M23" s="1">
-        <v>0</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C24" s="1">
+      <c r="F37" s="1">
+        <v>1</v>
+      </c>
+      <c r="G37" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1</v>
+      </c>
+      <c r="I37" s="1">
+        <v>1</v>
+      </c>
+      <c r="J37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37" s="1">
+        <v>0</v>
+      </c>
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <v>0</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C38" s="1">
         <v>102</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E24" s="1">
+      <c r="D38" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E38" s="1">
         <v>2</v>
       </c>
-      <c r="F24" s="1">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H24" s="1">
-        <v>1</v>
-      </c>
-      <c r="I24" s="1">
-        <v>1</v>
-      </c>
-      <c r="J24" s="1">
-        <v>1</v>
-      </c>
-      <c r="K24" s="1">
-        <v>0</v>
-      </c>
-      <c r="L24" s="1">
+      <c r="F38" s="1">
+        <v>1</v>
+      </c>
+      <c r="G38" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="1">
+        <v>1</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0</v>
+      </c>
+      <c r="L38" s="1">
         <v>100</v>
       </c>
-      <c r="M24" s="1">
-        <v>0</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C25" s="1">
+      <c r="M38" s="1">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C39" s="1">
         <v>103</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E25" s="1">
+      <c r="D39" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E39" s="1">
         <v>2</v>
       </c>
-      <c r="F25" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G25" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H25" s="1">
-        <v>1</v>
-      </c>
-      <c r="I25" s="1">
+      <c r="F39" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G39" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H39" s="1">
+        <v>1</v>
+      </c>
+      <c r="I39" s="1">
         <v>2</v>
       </c>
-      <c r="J25" s="1">
-        <v>1</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0</v>
-      </c>
-      <c r="L25" s="1">
-        <v>0</v>
-      </c>
-      <c r="M25" s="1">
-        <v>0</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C26" s="1">
+      <c r="J39" s="1">
+        <v>1</v>
+      </c>
+      <c r="K39" s="1">
+        <v>0</v>
+      </c>
+      <c r="L39" s="1">
+        <v>0</v>
+      </c>
+      <c r="M39" s="1">
+        <v>0</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O39" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C40" s="1">
         <v>104</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E26" s="1">
+      <c r="D40" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40" s="1">
         <v>2</v>
       </c>
-      <c r="F26" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G26" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H26" s="1">
-        <v>1</v>
-      </c>
-      <c r="I26" s="1">
+      <c r="F40" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G40" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H40" s="1">
+        <v>1</v>
+      </c>
+      <c r="I40" s="1">
         <v>2</v>
       </c>
-      <c r="J26" s="1">
-        <v>1</v>
-      </c>
-      <c r="K26" s="1">
-        <v>0</v>
-      </c>
-      <c r="L26" s="1">
-        <v>0</v>
-      </c>
-      <c r="M26" s="1">
-        <v>0</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C27" s="1">
+      <c r="J40" s="1">
+        <v>1</v>
+      </c>
+      <c r="K40" s="1">
+        <v>0</v>
+      </c>
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40" s="1">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C41" s="1">
         <v>107</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E27" s="1">
+      <c r="D41" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" s="1">
         <v>2</v>
       </c>
-      <c r="F27" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G27" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H27" s="1">
-        <v>1</v>
-      </c>
-      <c r="I27" s="1">
+      <c r="F41" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G41" s="1">
+        <v>-1</v>
+      </c>
+      <c r="H41" s="1">
+        <v>1</v>
+      </c>
+      <c r="I41" s="1">
         <v>2</v>
       </c>
-      <c r="J27" s="1">
-        <v>1</v>
-      </c>
-      <c r="K27" s="1">
-        <v>0</v>
-      </c>
-      <c r="L27" s="1">
-        <v>0</v>
-      </c>
-      <c r="M27" s="1">
-        <v>0</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C28" s="1">
+      <c r="J41" s="1">
+        <v>1</v>
+      </c>
+      <c r="K41" s="1">
+        <v>0</v>
+      </c>
+      <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <v>0</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C42" s="1">
         <v>109</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E28" s="1">
+      <c r="D42" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="1">
         <v>2</v>
       </c>
-      <c r="F28" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G28" s="1">
-        <v>0</v>
-      </c>
-      <c r="H28" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I28" s="1">
+      <c r="F42" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G42" s="1">
+        <v>0</v>
+      </c>
+      <c r="H42" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I42" s="1">
         <v>2</v>
       </c>
-      <c r="J28" s="1">
-        <v>0</v>
-      </c>
-      <c r="K28" s="1">
-        <v>0</v>
-      </c>
-      <c r="L28" s="1">
-        <v>0</v>
-      </c>
-      <c r="M28" s="1">
-        <v>0</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="O28" s="2"/>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C29" s="1">
+      <c r="J42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="L42" s="1">
+        <v>0</v>
+      </c>
+      <c r="M42" s="1">
+        <v>0</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="O42" s="2"/>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C43" s="1">
         <v>110</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E29" s="1">
+      <c r="D43" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E43" s="1">
         <v>2</v>
       </c>
-      <c r="F29" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G29" s="1">
-        <v>1</v>
-      </c>
-      <c r="H29" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I29" s="1">
+      <c r="F43" s="1">
+        <v>-1</v>
+      </c>
+      <c r="G43" s="1">
+        <v>1</v>
+      </c>
+      <c r="H43" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I43" s="1">
         <v>2</v>
       </c>
-      <c r="J29" s="1">
-        <v>0</v>
-      </c>
-      <c r="K29" s="1">
-        <v>0</v>
-      </c>
-      <c r="L29" s="1">
-        <v>0</v>
-      </c>
-      <c r="M29" s="1">
-        <v>0</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="O29" s="2"/>
-    </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C30" s="1">
+      <c r="J43" s="1">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
+        <v>0</v>
+      </c>
+      <c r="L43" s="1">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
+        <v>0</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O43" s="2"/>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C44" s="1">
         <v>111</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E30" s="1">
+      <c r="D44" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E44" s="1">
         <v>2</v>
       </c>
-      <c r="F30" s="1">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1">
-        <v>1</v>
-      </c>
-      <c r="H30" s="1">
-        <v>1</v>
-      </c>
-      <c r="I30" s="1">
-        <v>1</v>
-      </c>
-      <c r="J30" s="1">
-        <v>1</v>
-      </c>
-      <c r="K30" s="1">
-        <v>0</v>
-      </c>
-      <c r="L30" s="1">
-        <v>0</v>
-      </c>
-      <c r="M30" s="1">
-        <v>0</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="O30" s="2"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="4:15">
-      <c r="D31" s="2"/>
-      <c r="O31" s="2"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C32" s="1">
+      <c r="F44" s="1">
+        <v>1</v>
+      </c>
+      <c r="G44" s="1">
+        <v>1</v>
+      </c>
+      <c r="H44" s="1">
+        <v>1</v>
+      </c>
+      <c r="I44" s="1">
+        <v>1</v>
+      </c>
+      <c r="J44" s="1">
+        <v>1</v>
+      </c>
+      <c r="K44" s="1">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>0</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="O44" s="2"/>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="4:15">
+      <c r="D45" s="2"/>
+      <c r="O45" s="2"/>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C46" s="1">
         <v>305</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E32" s="1">
+      <c r="D46" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E46" s="1">
         <v>3</v>
       </c>
-      <c r="F32" s="1">
-        <v>0</v>
-      </c>
-      <c r="G32" s="1">
+      <c r="F46" s="1">
+        <v>0</v>
+      </c>
+      <c r="G46" s="1">
         <v>-2</v>
       </c>
-      <c r="H32" s="1">
-        <v>1</v>
-      </c>
-      <c r="I32" s="1">
+      <c r="H46" s="1">
+        <v>1</v>
+      </c>
+      <c r="I46" s="1">
         <v>2</v>
       </c>
-      <c r="J32" s="1">
-        <v>1</v>
-      </c>
-      <c r="K32" s="1">
-        <v>-1</v>
-      </c>
-      <c r="L32" s="1">
-        <v>0</v>
-      </c>
-      <c r="M32" s="1">
-        <v>0</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C33" s="1">
+      <c r="J46" s="1">
+        <v>1</v>
+      </c>
+      <c r="K46" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L46" s="1">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="O46" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C47" s="1">
         <v>306</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E33" s="1">
+      <c r="D47" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E47" s="1">
         <v>3</v>
       </c>
-      <c r="F33" s="1">
-        <v>0</v>
-      </c>
-      <c r="G33" s="1">
+      <c r="F47" s="1">
+        <v>0</v>
+      </c>
+      <c r="G47" s="1">
         <v>-2</v>
       </c>
-      <c r="H33" s="1">
-        <v>1</v>
-      </c>
-      <c r="I33" s="1">
+      <c r="H47" s="1">
+        <v>1</v>
+      </c>
+      <c r="I47" s="1">
         <v>2</v>
       </c>
-      <c r="J33" s="1">
-        <v>1</v>
-      </c>
-      <c r="K33" s="1">
-        <v>-1</v>
-      </c>
-      <c r="L33" s="1">
-        <v>0</v>
-      </c>
-      <c r="M33" s="1">
-        <v>0</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:15">
-      <c r="C35" s="1">
+      <c r="J47" s="1">
+        <v>1</v>
+      </c>
+      <c r="K47" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L47" s="1">
+        <v>0</v>
+      </c>
+      <c r="M47" s="1">
+        <v>0</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="O47" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C48" s="1">
+        <v>307</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E48" s="1">
+        <v>3</v>
+      </c>
+      <c r="F48" s="1">
+        <v>0</v>
+      </c>
+      <c r="G48" s="1">
+        <v>-2</v>
+      </c>
+      <c r="H48" s="1">
+        <v>1</v>
+      </c>
+      <c r="I48" s="1">
+        <v>2</v>
+      </c>
+      <c r="J48" s="1">
+        <v>1</v>
+      </c>
+      <c r="K48" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L48" s="1">
+        <v>0</v>
+      </c>
+      <c r="M48" s="1">
+        <v>0</v>
+      </c>
+      <c r="N48" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="O49" s="2"/>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:15">
+      <c r="C50" s="1">
         <v>401</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E35" s="1">
+      <c r="D50" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E50" s="1">
         <v>4</v>
       </c>
-      <c r="F35" s="1">
-        <v>1</v>
-      </c>
-      <c r="G35" s="1">
+      <c r="F50" s="1">
+        <v>1</v>
+      </c>
+      <c r="G50" s="1">
         <v>-2</v>
       </c>
-      <c r="H35" s="1">
-        <v>-1</v>
-      </c>
-      <c r="I35" s="1">
-        <v>1</v>
-      </c>
-      <c r="J35" s="1">
-        <v>0</v>
-      </c>
-      <c r="K35" s="1">
-        <v>-1</v>
-      </c>
-      <c r="L35" s="1">
-        <v>0</v>
-      </c>
-      <c r="M35" s="1">
-        <v>0</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:14">
-      <c r="C37" s="2">
+      <c r="H50" s="1">
+        <v>-1</v>
+      </c>
+      <c r="I50" s="1">
+        <v>1</v>
+      </c>
+      <c r="J50" s="1">
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L50" s="1">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
+        <v>0</v>
+      </c>
+      <c r="O50" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" customHeight="1" spans="3:14">
+      <c r="C52" s="2">
         <v>500</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E37" s="2">
+      <c r="D52" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E52" s="2">
         <v>5</v>
       </c>
-      <c r="F37" s="2">
-        <v>0</v>
-      </c>
-      <c r="G37" s="2">
-        <v>0</v>
-      </c>
-      <c r="H37" s="2">
-        <v>0</v>
-      </c>
-      <c r="I37" s="2">
-        <v>0</v>
-      </c>
-      <c r="J37" s="2">
-        <v>0</v>
-      </c>
-      <c r="K37" s="2">
-        <v>0</v>
-      </c>
-      <c r="L37" s="2">
-        <v>0</v>
-      </c>
-      <c r="M37" s="2">
-        <v>0</v>
-      </c>
-      <c r="N37" s="2" t="s">
-        <v>88</v>
+      <c r="F52" s="2">
+        <v>0</v>
+      </c>
+      <c r="G52" s="2">
+        <v>0</v>
+      </c>
+      <c r="H52" s="2">
+        <v>0</v>
+      </c>
+      <c r="I52" s="2">
+        <v>0</v>
+      </c>
+      <c r="J52" s="2">
+        <v>0</v>
+      </c>
+      <c r="K52" s="2">
+        <v>0</v>
+      </c>
+      <c r="L52" s="2">
+        <v>0</v>
+      </c>
+      <c r="M52" s="2">
+        <v>0</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:C5 F3:F5 H3:H5 N3:N5 D3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="H3:H5 N3:N5 C3:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="44">
   <si>
     <t>#</t>
   </si>
@@ -164,15 +164,18 @@
     <t>Before</t>
   </si>
   <si>
+    <t>Enemy</t>
+  </si>
+  <si>
+    <t>削减敌人固定护甲值，比如-1点</t>
+  </si>
+  <si>
+    <t>降低敌人护甲倍率</t>
+  </si>
+  <si>
     <t>enemy</t>
   </si>
   <si>
-    <t>削减敌人固定护甲值，比如-1点</t>
-  </si>
-  <si>
-    <t>降低敌人护甲倍率</t>
-  </si>
-  <si>
     <t>削减敌人护甲倍率，比如扣掉20%护甲</t>
   </si>
   <si>
@@ -182,7 +185,7 @@
     <t>Afer</t>
   </si>
   <si>
-    <t>self</t>
+    <t>Self</t>
   </si>
   <si>
     <t>吸血1%</t>
@@ -412,12 +415,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1213,22 +1216,18 @@
     <col min="7" max="7" width="10.5" style="2" customWidth="1"/>
     <col min="8" max="8" width="10" style="2" customWidth="1"/>
     <col min="9" max="9" width="10.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="53" style="2" customWidth="1"/>
-    <col min="11" max="11" width="16.25" style="2" customWidth="1"/>
+    <col min="10" max="11" width="53" style="2" customWidth="1"/>
     <col min="12" max="16380" width="9" style="2"/>
     <col min="16382" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="3:11">
       <c r="G1" s="3"/>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="3:11">
-      <c r="J2" s="2" t="s">
-        <v>0</v>
-      </c>
       <c r="K2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1258,6 +1257,9 @@
       <c r="J3" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="K3" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="4" customHeight="1" spans="3:11">
       <c r="C4" s="4" t="s">
@@ -1284,6 +1286,9 @@
       <c r="J4" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="K4" s="4" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="5" customHeight="1" spans="3:11">
       <c r="C5" s="4" t="s">
@@ -1310,6 +1315,9 @@
       <c r="J5" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="K5" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C6" s="1">
@@ -1334,7 +1342,9 @@
       <c r="J6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="2"/>
+      <c r="K6" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C7" s="1">
@@ -1351,25 +1361,27 @@
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I7" s="1">
         <v>-10002</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="K7" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8" s="1">
         <v>2</v>
@@ -1378,22 +1390,24 @@
         <v>1</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K8" s="2"/>
+        <v>29</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>20</v>
@@ -1409,16 +1423,18 @@
         <v>11</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="2"/>
+        <v>31</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>20</v>
@@ -1436,16 +1452,18 @@
         <v>-1</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10" s="2"/>
+        <v>33</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>20</v>
@@ -1461,7 +1479,10 @@
         <v>-10029</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1469,7 +1490,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>20</v>
@@ -1479,22 +1500,24 @@
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I12" s="1">
         <v>10027</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K12" s="2"/>
+        <v>37</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>20</v>
@@ -1504,22 +1527,24 @@
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I13" s="1">
         <v>2</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K13" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>20</v>
@@ -1529,78 +1554,62 @@
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I14" s="1">
         <v>10028</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="K14" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="2"/>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="2"/>
     </row>
     <row r="17" customHeight="1" spans="3:11">
       <c r="C17" s="1"/>
-      <c r="D17" s="2"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
     <row r="18" customHeight="1" spans="3:11">
       <c r="C18" s="1"/>
-      <c r="D18" s="2"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
     <row r="19" customHeight="1" spans="3:11">
       <c r="C19" s="1"/>
-      <c r="D19" s="2"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
     <row r="20" customHeight="1" spans="3:11">
       <c r="C20" s="1"/>
-      <c r="D20" s="2"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="K21" s="2"/>
     </row>
     <row r="22" customHeight="1" spans="3:11">
       <c r="C22" s="1">
         <v>1001</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="23" customFormat="1" customHeight="1" spans="3:11">
@@ -1761,106 +1770,48 @@
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="K38" s="2"/>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="2"/>
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="K40" s="2"/>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="K41" s="2"/>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="2"/>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="2"/>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="2"/>
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
-      <c r="K45" s="2"/>
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="2"/>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="2"/>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="2"/>
-    </row>
-    <row r="49" customFormat="1" customHeight="1" spans="3:11">
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="3:9">
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -1868,15 +1819,14 @@
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
-      <c r="K49" s="2"/>
-    </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:11">
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:9">
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:E5 F3:F5 J3:J5 C3:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="J3:J5 K3:K5 C3:F5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -30,6 +30,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
+    <author>Administrator</author>
   </authors>
   <commentList>
     <comment ref="C3" authorId="0">
@@ -94,12 +95,37 @@
         </r>
       </text>
     </comment>
+    <comment ref="H3" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 self
+2 enemy
+3 skill
+4 valet</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="43">
   <si>
     <t>#</t>
   </si>
@@ -164,18 +190,12 @@
     <t>Before</t>
   </si>
   <si>
-    <t>Enemy</t>
-  </si>
-  <si>
     <t>削减敌人固定护甲值，比如-1点</t>
   </si>
   <si>
     <t>降低敌人护甲倍率</t>
   </si>
   <si>
-    <t>enemy</t>
-  </si>
-  <si>
     <t>削减敌人护甲倍率，比如扣掉20%护甲</t>
   </si>
   <si>
@@ -185,9 +205,6 @@
     <t>Afer</t>
   </si>
   <si>
-    <t>Self</t>
-  </si>
-  <si>
     <t>吸血1%</t>
   </si>
   <si>
@@ -225,6 +242,12 @@
   </si>
   <si>
     <t>给加额外免伤10%，倍率诚阿福</t>
+  </si>
+  <si>
+    <t>麻痹</t>
+  </si>
+  <si>
+    <t>免控</t>
   </si>
   <si>
     <t>宠物继承人物的神符技能</t>
@@ -415,12 +438,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1307,7 +1330,7 @@
         <v>17</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>17</v>
@@ -1333,17 +1356,17 @@
         <v>1</v>
       </c>
       <c r="G6" s="1"/>
-      <c r="H6" s="1" t="s">
-        <v>21</v>
+      <c r="H6" s="1">
+        <v>2</v>
       </c>
       <c r="I6" s="1">
         <v>2</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1351,7 +1374,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>20</v>
@@ -1360,17 +1383,17 @@
         <v>1</v>
       </c>
       <c r="G7" s="1"/>
-      <c r="H7" s="1" t="s">
-        <v>24</v>
+      <c r="H7" s="1">
+        <v>2</v>
       </c>
       <c r="I7" s="1">
         <v>-10002</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1378,10 +1401,10 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1">
         <v>2</v>
@@ -1389,17 +1412,17 @@
       <c r="G8" s="1">
         <v>1</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>28</v>
+      <c r="H8" s="1">
+        <v>1</v>
       </c>
       <c r="I8" s="1">
         <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1407,7 +1430,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>20</v>
@@ -1416,17 +1439,17 @@
         <v>1</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="H9" s="1" t="s">
-        <v>21</v>
+      <c r="H9" s="1">
+        <v>2</v>
       </c>
       <c r="I9" s="1">
         <v>11</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1434,28 +1457,28 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F10" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
         <v>1</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>21</v>
+      <c r="H10" s="1">
+        <v>2</v>
       </c>
       <c r="I10" s="1">
         <v>-1</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1463,7 +1486,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>20</v>
@@ -1472,17 +1495,17 @@
         <v>1</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="H11" s="1" t="s">
-        <v>21</v>
+      <c r="H11" s="1">
+        <v>2</v>
       </c>
       <c r="I11" s="1">
         <v>-10029</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1490,7 +1513,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>20</v>
@@ -1499,17 +1522,17 @@
         <v>1</v>
       </c>
       <c r="G12" s="1"/>
-      <c r="H12" s="1" t="s">
-        <v>28</v>
+      <c r="H12" s="1">
+        <v>1</v>
       </c>
       <c r="I12" s="1">
         <v>10027</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1517,7 +1540,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>20</v>
@@ -1526,17 +1549,17 @@
         <v>1</v>
       </c>
       <c r="G13" s="1"/>
-      <c r="H13" s="1" t="s">
-        <v>28</v>
+      <c r="H13" s="1">
+        <v>1</v>
       </c>
       <c r="I13" s="1">
         <v>2</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1544,7 +1567,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>20</v>
@@ -1553,17 +1576,17 @@
         <v>1</v>
       </c>
       <c r="G14" s="1"/>
-      <c r="H14" s="1" t="s">
-        <v>28</v>
+      <c r="H14" s="1">
+        <v>1</v>
       </c>
       <c r="I14" s="1">
         <v>10028</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:11">
@@ -1590,26 +1613,44 @@
       <c r="G19" s="1"/>
     </row>
     <row r="20" customHeight="1" spans="3:11">
-      <c r="C20" s="1"/>
-      <c r="F20" s="1"/>
+      <c r="C20" s="1">
+        <v>901</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F20" s="1">
+        <v>3</v>
+      </c>
       <c r="G20" s="1"/>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="D21" s="2"/>
+      <c r="C21" s="1">
+        <v>902</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="E21" s="2"/>
+      <c r="F21" s="1">
+        <v>4</v>
+      </c>
     </row>
     <row r="22" customHeight="1" spans="3:11">
       <c r="C22" s="1">
         <v>1001</v>
       </c>
       <c r="D22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="1">
+        <v>1001</v>
+      </c>
+      <c r="J22" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="J22" s="2" t="s">
-        <v>43</v>
-      </c>
       <c r="K22" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" customFormat="1" customHeight="1" spans="3:11">
@@ -1826,7 +1867,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="J3:J5 K3:K5 C3:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5 J3:K5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="42">
   <si>
     <t>#</t>
   </si>
@@ -190,13 +190,10 @@
     <t>Before</t>
   </si>
   <si>
-    <t>削减敌人固定护甲值，比如-1点</t>
-  </si>
-  <si>
-    <t>降低敌人护甲倍率</t>
-  </si>
-  <si>
-    <t>削减敌人护甲倍率，比如扣掉20%护甲</t>
+    <t>削减敌人{1}%的护甲</t>
+  </si>
+  <si>
+    <t>不同来源乘法</t>
   </si>
   <si>
     <t>伤害百分比吸血</t>
@@ -235,13 +232,13 @@
     <t>增加自己固定护甲</t>
   </si>
   <si>
-    <t>削减敌人固定护甲值，比如100点</t>
+    <t>增加自己{1}的护甲倍率</t>
   </si>
   <si>
     <t>给自己免伤</t>
   </si>
   <si>
-    <t>给加额外免伤10%，倍率诚阿福</t>
+    <t>增加自己{1}的免伤倍率</t>
   </si>
   <si>
     <t>麻痹</t>
@@ -1230,7 +1227,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:K50"/>
+  <dimension ref="C1:K49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -1360,133 +1357,133 @@
         <v>2</v>
       </c>
       <c r="I6" s="1">
-        <v>2</v>
+        <v>-10002</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>21</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="1">
         <v>2</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>1</v>
       </c>
-      <c r="G7" s="1"/>
       <c r="H7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" s="1">
-        <v>-10002</v>
+        <v>1</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C8" s="1">
-        <v>3</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F8" s="1">
+        <v>1</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1">
         <v>2</v>
       </c>
-      <c r="G8" s="1">
-        <v>1</v>
-      </c>
-      <c r="H8" s="1">
-        <v>1</v>
-      </c>
       <c r="I8" s="1">
-        <v>1</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>26</v>
+        <v>11</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C9" s="1">
-        <v>4</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>27</v>
+        <v>5</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>28</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F9" s="1">
+        <v>5</v>
+      </c>
+      <c r="G9" s="1">
         <v>1</v>
       </c>
-      <c r="G9" s="1"/>
       <c r="H9" s="1">
         <v>2</v>
       </c>
       <c r="I9" s="1">
-        <v>11</v>
+        <v>-1</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C10" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F10" s="1">
-        <v>5</v>
-      </c>
-      <c r="G10" s="1">
         <v>1</v>
       </c>
+      <c r="G10" s="1"/>
       <c r="H10" s="1">
         <v>2</v>
       </c>
       <c r="I10" s="1">
-        <v>-1</v>
+        <v>-10029</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C11" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>20</v>
@@ -1496,24 +1493,24 @@
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" s="1">
-        <v>-10029</v>
+        <v>10027</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C12" s="1">
-        <v>7</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>20</v>
@@ -1526,21 +1523,21 @@
         <v>1</v>
       </c>
       <c r="I12" s="1">
-        <v>10027</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>34</v>
+        <v>10002</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C13" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>20</v>
@@ -1553,49 +1550,27 @@
         <v>1</v>
       </c>
       <c r="I13" s="1">
-        <v>2</v>
+        <v>10028</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C14" s="1">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1">
-        <v>1</v>
-      </c>
-      <c r="I14" s="1">
-        <v>10028</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:11">
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
+    <row r="16" customHeight="1" spans="3:11">
+      <c r="C16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
     </row>
     <row r="17" customHeight="1" spans="3:11">
       <c r="C17" s="1"/>
@@ -1608,50 +1583,56 @@
       <c r="G18" s="1"/>
     </row>
     <row r="19" customHeight="1" spans="3:11">
-      <c r="C19" s="1"/>
-      <c r="F19" s="1"/>
+      <c r="C19" s="1">
+        <v>901</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="1">
+        <v>3</v>
+      </c>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" customHeight="1" spans="3:11">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="C20" s="1">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>39</v>
       </c>
+      <c r="E20" s="2"/>
       <c r="F20" s="1">
-        <v>3</v>
-      </c>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="3:11">
       <c r="C21" s="1">
-        <v>902</v>
+        <v>1001</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="2"/>
       <c r="F21" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:11">
-      <c r="C22" s="1">
         <v>1001</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="J21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="1">
-        <v>1001</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>42</v>
-      </c>
+      <c r="K21" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C22" s="1"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
     </row>
     <row r="23" customFormat="1" customHeight="1" spans="3:11">
       <c r="C23" s="1"/>
@@ -1676,7 +1657,7 @@
       <c r="K24" s="2"/>
     </row>
     <row r="25" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C25" s="1"/>
+      <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
@@ -1796,18 +1777,11 @@
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
     </row>
-    <row r="36" customFormat="1" customHeight="1" spans="3:11">
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-    </row>
-    <row r="37" s="1" customFormat="1" customHeight="1"/>
+    <row r="36" s="1" customFormat="1" customHeight="1"/>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+    </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
@@ -1848,22 +1822,18 @@
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="48" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
-    </row>
-    <row r="49" customFormat="1" customHeight="1" spans="3:9">
-      <c r="C49" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+    </row>
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="4:5">
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="2"/>
-    </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:9">
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0">
+    <comment ref="G3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -71,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -95,7 +95,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="1">
+    <comment ref="I3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -125,7 +125,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="46">
   <si>
     <t>#</t>
   </si>
@@ -139,6 +139,9 @@
     <t>计算顺序</t>
   </si>
   <si>
+    <t>运行周期</t>
+  </si>
+  <si>
     <t>类型</t>
   </si>
   <si>
@@ -160,7 +163,10 @@
     <t>Name</t>
   </si>
   <si>
-    <t>RunType</t>
+    <t>StartType</t>
+  </si>
+  <si>
+    <t>RunCycle</t>
   </si>
   <si>
     <t>Type</t>
@@ -190,6 +196,9 @@
     <t>Before</t>
   </si>
   <si>
+    <t>Single</t>
+  </si>
+  <si>
     <t>削减敌人{1}%的护甲</t>
   </si>
   <si>
@@ -199,7 +208,7 @@
     <t>伤害百分比吸血</t>
   </si>
   <si>
-    <t>Afer</t>
+    <t>After</t>
   </si>
   <si>
     <t>吸血1%</t>
@@ -212,6 +221,9 @@
   </si>
   <si>
     <t>持续掉血</t>
+  </si>
+  <si>
+    <t>Interval</t>
   </si>
   <si>
     <t>按伤害持续掉血，比如流血20%伤害，灼烧10%伤害</t>
@@ -1227,32 +1239,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:K49"/>
+  <dimension ref="C1:L49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
-    <col min="4" max="5" width="17.25" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.75" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.5" style="2" customWidth="1"/>
-    <col min="8" max="8" width="10" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.25" style="2" customWidth="1"/>
-    <col min="10" max="11" width="53" style="2" customWidth="1"/>
-    <col min="12" max="16380" width="9" style="2"/>
-    <col min="16382" max="16384" width="9" style="2"/>
+    <col min="4" max="6" width="17.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.75" style="2" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10" style="2" customWidth="1"/>
+    <col min="10" max="10" width="10.25" style="2" customWidth="1"/>
+    <col min="11" max="12" width="53" style="2" customWidth="1"/>
+    <col min="13" max="16381" width="9" style="2"/>
+    <col min="16383" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:11">
-      <c r="G1" s="3"/>
-      <c r="K1" s="2" t="s">
+    <row r="1" customHeight="1" spans="3:12">
+      <c r="H1" s="3"/>
+      <c r="L1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customHeight="1" spans="3:11">
-      <c r="K2" s="2" t="s">
+    <row r="2" customHeight="1" spans="3:12">
+      <c r="L2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="3:11">
+    <row r="3" customHeight="1" spans="3:12">
       <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1278,109 +1290,121 @@
         <v>8</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="3:11">
+        <v>9</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="3:12">
       <c r="C4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="3:11">
+        <v>18</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="3:12">
       <c r="C5" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:11">
+        <v>20</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="1">
+        <v>22</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="1">
         <v>1</v>
       </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1">
+      <c r="H6" s="1"/>
+      <c r="I6" s="1">
         <v>2</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>-10002</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="K6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:11">
+        <v>24</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C7" s="1">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>2</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
@@ -1388,242 +1412,266 @@
       <c r="I7" s="1">
         <v>1</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>25</v>
+      <c r="J7" s="1">
+        <v>1</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:11">
+        <v>28</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C8" s="1">
         <v>4</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="1">
+        <v>22</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="1">
         <v>1</v>
       </c>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1">
+      <c r="H8" s="1"/>
+      <c r="I8" s="1">
         <v>2</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>11</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>27</v>
-      </c>
       <c r="K8" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:11">
+        <v>30</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C9" s="1">
         <v>5</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="1">
+        <v>27</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G9" s="1">
         <v>5</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>1</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>2</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>-1</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="K9" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:11">
+        <v>33</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C10" s="1">
         <v>6</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="1">
+        <v>22</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="1">
         <v>1</v>
       </c>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1">
+      <c r="H10" s="1"/>
+      <c r="I10" s="1">
         <v>2</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>-10029</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="K10" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:11">
+        <v>35</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C11" s="1">
         <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="1">
+        <v>22</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G11" s="1">
         <v>1</v>
       </c>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1">
+      <c r="H11" s="1"/>
+      <c r="I11" s="1">
         <v>1</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>10027</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="K11" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:11">
+        <v>37</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C12" s="1">
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="1">
+        <v>22</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G12" s="1">
         <v>1</v>
       </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1">
+      <c r="H12" s="1"/>
+      <c r="I12" s="1">
         <v>1</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <v>10002</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="K12" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:11">
+        <v>39</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C13" s="1">
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="1">
+        <v>22</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="1">
         <v>1</v>
       </c>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1">
+      <c r="H13" s="1"/>
+      <c r="I13" s="1">
         <v>1</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <v>10028</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="K13" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:11">
+        <v>41</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="F14" s="2"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-    </row>
-    <row r="16" customHeight="1" spans="3:11">
+      <c r="F15" s="2"/>
+    </row>
+    <row r="16" customHeight="1" spans="3:12">
       <c r="C16" s="1"/>
-      <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-    </row>
-    <row r="17" customHeight="1" spans="3:11">
+      <c r="H16" s="1"/>
+    </row>
+    <row r="17" customHeight="1" spans="3:12">
       <c r="C17" s="1"/>
-      <c r="F17" s="1"/>
       <c r="G17" s="1"/>
-    </row>
-    <row r="18" customHeight="1" spans="3:11">
+      <c r="H17" s="1"/>
+    </row>
+    <row r="18" customHeight="1" spans="3:12">
       <c r="C18" s="1"/>
-      <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-    </row>
-    <row r="19" customHeight="1" spans="3:11">
+      <c r="H18" s="1"/>
+    </row>
+    <row r="19" customHeight="1" spans="3:12">
       <c r="C19" s="1">
         <v>901</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" s="1">
+        <v>42</v>
+      </c>
+      <c r="G19" s="1">
         <v>3</v>
       </c>
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="H19" s="1"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C20" s="1">
         <v>902</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E20" s="2"/>
-      <c r="F20" s="1">
+      <c r="F20" s="2"/>
+      <c r="G20" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="21" customHeight="1" spans="3:11">
+    <row r="21" customHeight="1" spans="3:12">
       <c r="C21" s="1">
         <v>1001</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="1">
+        <v>44</v>
+      </c>
+      <c r="G21" s="1">
         <v>1001</v>
       </c>
-      <c r="J21" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="K21" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" customHeight="1" spans="3:11">
+        <v>45</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" customHeight="1" spans="3:12">
       <c r="C22" s="1"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -1633,8 +1681,9 @@
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
-    </row>
-    <row r="23" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L22" s="2"/>
+    </row>
+    <row r="23" customFormat="1" customHeight="1" spans="3:12">
       <c r="C23" s="1"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -1644,8 +1693,9 @@
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
-    </row>
-    <row r="24" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L23" s="2"/>
+    </row>
+    <row r="24" customFormat="1" customHeight="1" spans="3:12">
       <c r="C24" s="1"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -1655,8 +1705,9 @@
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-    </row>
-    <row r="25" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L24" s="2"/>
+    </row>
+    <row r="25" customFormat="1" customHeight="1" spans="3:12">
       <c r="C25" s="2"/>
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
@@ -1666,8 +1717,9 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
-    </row>
-    <row r="26" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L25" s="2"/>
+    </row>
+    <row r="26" customFormat="1" customHeight="1" spans="3:12">
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
@@ -1677,8 +1729,9 @@
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
-    </row>
-    <row r="27" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L26" s="2"/>
+    </row>
+    <row r="27" customFormat="1" customHeight="1" spans="3:12">
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
       <c r="E27" s="2"/>
@@ -1688,8 +1741,9 @@
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
-    </row>
-    <row r="28" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L27" s="2"/>
+    </row>
+    <row r="28" customFormat="1" customHeight="1" spans="3:12">
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
@@ -1699,8 +1753,9 @@
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
-    </row>
-    <row r="29" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L28" s="2"/>
+    </row>
+    <row r="29" customFormat="1" customHeight="1" spans="3:12">
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
@@ -1710,8 +1765,9 @@
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
-    </row>
-    <row r="30" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L29" s="2"/>
+    </row>
+    <row r="30" customFormat="1" customHeight="1" spans="3:12">
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
@@ -1721,8 +1777,9 @@
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
-    </row>
-    <row r="31" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L30" s="2"/>
+    </row>
+    <row r="31" customFormat="1" customHeight="1" spans="3:12">
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
@@ -1732,8 +1789,9 @@
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
-    </row>
-    <row r="32" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L31" s="2"/>
+    </row>
+    <row r="32" customFormat="1" customHeight="1" spans="3:12">
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -1743,8 +1801,9 @@
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
-    </row>
-    <row r="33" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L32" s="2"/>
+    </row>
+    <row r="33" customFormat="1" customHeight="1" spans="3:12">
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -1754,8 +1813,9 @@
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
-    </row>
-    <row r="34" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L33" s="2"/>
+    </row>
+    <row r="34" customFormat="1" customHeight="1" spans="3:12">
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
@@ -1765,8 +1825,9 @@
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
-    </row>
-    <row r="35" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L34" s="2"/>
+    </row>
+    <row r="35" customFormat="1" customHeight="1" spans="3:12">
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
@@ -1776,53 +1837,65 @@
       <c r="I35" s="2"/>
       <c r="J35" s="2"/>
       <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1"/>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="F37" s="2"/>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="F38" s="2"/>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="F39" s="2"/>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="F40" s="2"/>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
-    </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="F41" s="2"/>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
-    </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="F42" s="2"/>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
-    </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="F43" s="2"/>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
-    </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="F44" s="2"/>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
-    </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="F45" s="2"/>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
-    </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="F46" s="2"/>
+    </row>
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
-    </row>
-    <row r="48" customFormat="1" customHeight="1" spans="3:11">
+      <c r="F47" s="2"/>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="3:12">
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -1830,14 +1903,16 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
-    </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="4:5">
+      <c r="J48" s="2"/>
+    </row>
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="4:6">
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:F5 J3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5 K3:L5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G3" authorId="0">
+    <comment ref="H3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -71,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H3" authorId="0">
+    <comment ref="I3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -89,13 +89,12 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-0：无来源
-1：技能伤害
-2：属性</t>
+0：伤害
+&gt;0 ：属性ID</t>
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="1">
+    <comment ref="J3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -125,10 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="46">
-  <si>
-    <t>#</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="70">
   <si>
     <t>_Id</t>
   </si>
@@ -139,6 +135,9 @@
     <t>计算顺序</t>
   </si>
   <si>
+    <t>运行顺序</t>
+  </si>
+  <si>
     <t>运行周期</t>
   </si>
   <si>
@@ -166,19 +165,22 @@
     <t>StartType</t>
   </si>
   <si>
+    <t>RunSeq</t>
+  </si>
+  <si>
     <t>RunCycle</t>
   </si>
   <si>
     <t>Type</t>
   </si>
   <si>
-    <t>SourceAttr</t>
+    <t>SrcAtrId</t>
   </si>
   <si>
     <t>TargetType</t>
   </si>
   <si>
-    <t>TargetAttr</t>
+    <t>TarAtrId</t>
   </si>
   <si>
     <t>Des</t>
@@ -190,67 +192,136 @@
     <t>string</t>
   </si>
   <si>
-    <t>降低敌人固定护甲</t>
+    <t>攻击减护甲</t>
   </si>
   <si>
     <t>Before</t>
   </si>
   <si>
+    <t>Instantly</t>
+  </si>
+  <si>
     <t>Single</t>
   </si>
   <si>
-    <t>削减敌人{1}%的护甲</t>
-  </si>
-  <si>
-    <t>不同来源乘法</t>
-  </si>
-  <si>
-    <t>伤害百分比吸血</t>
+    <t>削减敌人{0}%的护甲，最高{2}层</t>
+  </si>
+  <si>
+    <t>禁疗</t>
+  </si>
+  <si>
+    <t>降低敌人治疗效果{0}%</t>
+  </si>
+  <si>
+    <t>减少敌人攻击速度</t>
+  </si>
+  <si>
+    <t>降低敌人{0}%的攻击速度</t>
+  </si>
+  <si>
+    <t>给敌人附加易伤</t>
+  </si>
+  <si>
+    <t>使敌人额外承伤{0}%，最高{2}层</t>
+  </si>
+  <si>
+    <t>给自己附加增伤</t>
+  </si>
+  <si>
+    <t>使自己额外增伤{0}%，最高{2}层</t>
+  </si>
+  <si>
+    <t>增加自己固定护甲</t>
+  </si>
+  <si>
+    <t>增加自己{1}的护甲倍率</t>
+  </si>
+  <si>
+    <t>给自己免伤</t>
+  </si>
+  <si>
+    <t>增加自己{1}的免伤倍率</t>
+  </si>
+  <si>
+    <t>攻击回复-按物攻</t>
   </si>
   <si>
     <t>After</t>
   </si>
   <si>
-    <t>吸血1%</t>
-  </si>
-  <si>
-    <t>减少敌人攻击速度</t>
-  </si>
-  <si>
-    <t>降低敌人20%的攻击速度</t>
-  </si>
-  <si>
-    <t>持续掉血</t>
+    <t>回复物攻{0}%的血量</t>
+  </si>
+  <si>
+    <t>攻击回复-按法攻</t>
+  </si>
+  <si>
+    <t>回复魔攻{0}%的血量</t>
+  </si>
+  <si>
+    <t>攻击回复-按道攻</t>
+  </si>
+  <si>
+    <t>回复道攻{0}%的血量</t>
+  </si>
+  <si>
+    <t>攻击回复-按防御</t>
+  </si>
+  <si>
+    <t>回复护甲{0}%的血量</t>
+  </si>
+  <si>
+    <t>攻击回复-按生命</t>
+  </si>
+  <si>
+    <t>回复最大生命{0}%的血量</t>
+  </si>
+  <si>
+    <t>攻击回复-按伤害</t>
+  </si>
+  <si>
+    <t>回复技能伤害{0}%的血量</t>
+  </si>
+  <si>
+    <t>持续伤害-按物攻</t>
+  </si>
+  <si>
+    <t>Delay</t>
   </si>
   <si>
     <t>Interval</t>
   </si>
   <si>
-    <t>按伤害持续掉血，比如流血20%伤害，灼烧10%伤害</t>
-  </si>
-  <si>
-    <t>给敌人附加易伤</t>
-  </si>
-  <si>
-    <t>敌人附加一个额外承受10%伤害的状态，最高3层</t>
-  </si>
-  <si>
-    <t>给自己附加增伤</t>
-  </si>
-  <si>
-    <t>自己附加一个额外增加5%伤害的状态，最高3层</t>
-  </si>
-  <si>
-    <t>增加自己固定护甲</t>
-  </si>
-  <si>
-    <t>增加自己{1}的护甲倍率</t>
-  </si>
-  <si>
-    <t>给自己免伤</t>
-  </si>
-  <si>
-    <t>增加自己{1}的免伤倍率</t>
+    <t>持续造成物攻{0}%的额外伤害</t>
+  </si>
+  <si>
+    <t>持续伤害-按法攻</t>
+  </si>
+  <si>
+    <t>持续造成魔攻{0}%的额外伤害</t>
+  </si>
+  <si>
+    <t>持续伤害-按道攻</t>
+  </si>
+  <si>
+    <t>持续造成道攻{0}%的额外伤害</t>
+  </si>
+  <si>
+    <t>持续伤害-按防御</t>
+  </si>
+  <si>
+    <t>持续造成护甲{0}%的额外伤害</t>
+  </si>
+  <si>
+    <t>持续伤害-按生命</t>
+  </si>
+  <si>
+    <t>持续造成最大生命{0}%的额外伤害</t>
+  </si>
+  <si>
+    <t>持续伤害-按伤害</t>
+  </si>
+  <si>
+    <t>持续造成技能额外伤害{0}%的额外伤害</t>
   </si>
   <si>
     <t>麻痹</t>
@@ -275,7 +346,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -299,6 +370,12 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
       <name val="等线"/>
       <charset val="134"/>
     </font>
@@ -447,12 +524,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -782,137 +859,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -920,6 +997,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1239,58 +1317,50 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:L49"/>
+  <dimension ref="C1:L61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
-    <col min="4" max="6" width="17.25" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.75" style="2" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10" style="2" customWidth="1"/>
-    <col min="10" max="10" width="10.25" style="2" customWidth="1"/>
-    <col min="11" max="12" width="53" style="2" customWidth="1"/>
+    <col min="4" max="7" width="17.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="10.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="10" style="2" customWidth="1"/>
+    <col min="11" max="11" width="10.25" style="2" customWidth="1"/>
+    <col min="12" max="12" width="53" style="2" customWidth="1"/>
     <col min="13" max="16381" width="9" style="2"/>
     <col min="16383" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="3:12">
-      <c r="H1" s="3"/>
-      <c r="L1" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" customHeight="1" spans="3:12">
-      <c r="L2" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="I1" s="3"/>
     </row>
     <row r="3" customHeight="1" spans="3:12">
       <c r="C3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>8</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>9</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>9</v>
@@ -1325,39 +1395,39 @@
         <v>18</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="3:12">
       <c r="C5" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>19</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:12">
@@ -1365,58 +1435,55 @@
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="1">
+      <c r="F6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="1">
         <v>1</v>
       </c>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1">
+      <c r="I6" s="1"/>
+      <c r="J6" s="1">
         <v>2</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>-10002</v>
       </c>
-      <c r="K6" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="L6" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C7" s="1">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>2</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="1">
-        <v>2</v>
+      <c r="F7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
       </c>
-      <c r="I7" s="1">
-        <v>1</v>
-      </c>
       <c r="J7" s="1">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>28</v>
+        <v>2</v>
+      </c>
+      <c r="K7" s="1">
+        <v>-10028</v>
       </c>
       <c r="L7" s="1" t="s">
         <v>28</v>
@@ -1430,23 +1497,23 @@
         <v>29</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="1">
+      <c r="F8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="1">
         <v>1</v>
       </c>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1">
+      <c r="I8" s="1"/>
+      <c r="J8" s="1">
         <v>2</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>11</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>30</v>
@@ -1454,369 +1521,571 @@
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C9" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="1">
-        <v>5</v>
+        <v>23</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="H9" s="1">
         <v>1</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="1"/>
+      <c r="J9" s="1">
         <v>2</v>
       </c>
-      <c r="J9" s="1">
-        <v>-1</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>33</v>
+      <c r="K9" s="1">
+        <v>-10029</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C10" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1">
+        <v>10027</v>
+      </c>
+      <c r="L10" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="1">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1">
-        <v>2</v>
-      </c>
-      <c r="J10" s="1">
-        <v>-10029</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C11" s="1">
-        <v>7</v>
-      </c>
-      <c r="D11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1">
+        <v>1</v>
+      </c>
+      <c r="K11" s="1">
+        <v>10002</v>
+      </c>
+      <c r="L11" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="1">
-        <v>1</v>
-      </c>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1">
-        <v>1</v>
-      </c>
-      <c r="J11" s="1">
-        <v>10027</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C12" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>10028</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G12" s="1">
-        <v>1</v>
-      </c>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1">
-        <v>1</v>
-      </c>
-      <c r="J12" s="1">
-        <v>10002</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>25</v>
-      </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C13" s="1">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="1">
-        <v>1</v>
-      </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1">
-        <v>1</v>
-      </c>
-      <c r="J13" s="1">
-        <v>10028</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-    </row>
-    <row r="16" customHeight="1" spans="3:12">
-      <c r="C16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-    </row>
-    <row r="17" customHeight="1" spans="3:12">
-      <c r="C17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-    </row>
-    <row r="18" customHeight="1" spans="3:12">
-      <c r="C18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-    </row>
-    <row r="19" customHeight="1" spans="3:12">
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C16" s="1">
+        <v>101</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H16" s="1">
+        <v>2</v>
+      </c>
+      <c r="I16" s="1">
+        <v>4</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1</v>
+      </c>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C17" s="1">
+        <v>102</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="1">
+        <v>2</v>
+      </c>
+      <c r="I17" s="1">
+        <v>5</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1</v>
+      </c>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C18" s="1">
+        <v>103</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1">
+        <v>2</v>
+      </c>
+      <c r="I18" s="1">
+        <v>6</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1</v>
+      </c>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C19" s="1">
-        <v>901</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G19" s="1">
-        <v>3</v>
-      </c>
-      <c r="H19" s="1"/>
+        <v>104</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H19" s="1">
+        <v>2</v>
+      </c>
+      <c r="I19" s="1">
+        <v>2</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1</v>
+      </c>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C20" s="1">
-        <v>902</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:12">
+        <v>105</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="1">
+        <v>2</v>
+      </c>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="J20" s="1">
+        <v>1</v>
+      </c>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C21" s="1">
-        <v>1001</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G21" s="1">
-        <v>1001</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C22" s="1"/>
+        <v>106</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="1">
+        <v>2</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>1</v>
+      </c>
+      <c r="L21" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-    </row>
-    <row r="23" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C23" s="1"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-    </row>
-    <row r="24" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C24" s="1"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-    </row>
-    <row r="25" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-    </row>
-    <row r="26" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-    </row>
-    <row r="27" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-    </row>
-    <row r="28" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-    </row>
-    <row r="29" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-    </row>
-    <row r="30" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-    </row>
-    <row r="31" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-    </row>
-    <row r="32" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C23" s="1">
+        <v>201</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H23" s="1">
+        <v>5</v>
+      </c>
+      <c r="I23" s="1">
+        <v>4</v>
+      </c>
+      <c r="J23" s="1">
+        <v>2</v>
+      </c>
+      <c r="K23" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C24" s="1">
+        <v>202</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H24" s="1">
+        <v>5</v>
+      </c>
+      <c r="I24" s="1">
+        <v>5</v>
+      </c>
+      <c r="J24" s="1">
+        <v>2</v>
+      </c>
+      <c r="K24" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:12">
+      <c r="C25" s="1">
+        <v>203</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H25" s="1">
+        <v>5</v>
+      </c>
+      <c r="I25" s="1">
+        <v>6</v>
+      </c>
+      <c r="J25" s="1">
+        <v>2</v>
+      </c>
+      <c r="K25" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:12">
+      <c r="C26" s="1">
+        <v>204</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H26" s="1">
+        <v>5</v>
+      </c>
+      <c r="I26" s="1">
+        <v>2</v>
+      </c>
+      <c r="J26" s="1">
+        <v>2</v>
+      </c>
+      <c r="K26" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:12">
+      <c r="C27" s="1">
+        <v>205</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H27" s="1">
+        <v>5</v>
+      </c>
+      <c r="I27" s="1">
+        <v>1</v>
+      </c>
+      <c r="J27" s="1">
+        <v>2</v>
+      </c>
+      <c r="K27" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:12">
+      <c r="C28" s="1">
+        <v>206</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H28" s="1">
+        <v>5</v>
+      </c>
+      <c r="I28" s="1">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1">
+        <v>2</v>
+      </c>
+      <c r="K28" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:12">
+      <c r="C29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" customHeight="1" spans="3:12">
+      <c r="C30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" customHeight="1" spans="3:12">
+      <c r="C31" s="1">
+        <v>901</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H31" s="1">
+        <v>3</v>
+      </c>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C32" s="1">
+        <v>902</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>67</v>
+      </c>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-    </row>
-    <row r="33" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
+      <c r="H32" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:12">
+      <c r="C33" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H33" s="1">
+        <v>1001</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="34" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C34" s="2"/>
+      <c r="C34" s="1"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
@@ -1828,7 +2097,7 @@
       <c r="L34" s="2"/>
     </row>
     <row r="35" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C35" s="2"/>
+      <c r="C35" s="1"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
@@ -1839,80 +2108,237 @@
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" s="1" customFormat="1" customHeight="1"/>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="36" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C36" s="1"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+    </row>
+    <row r="37" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+    </row>
+    <row r="38" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C38" s="2"/>
       <c r="D38" s="2"/>
       <c r="E38" s="2"/>
       <c r="F38" s="2"/>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+    </row>
+    <row r="39" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C39" s="2"/>
       <c r="D39" s="2"/>
       <c r="E39" s="2"/>
       <c r="F39" s="2"/>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+    </row>
+    <row r="40" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
       <c r="F40" s="2"/>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+    </row>
+    <row r="41" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-    </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+    </row>
+    <row r="42" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
-    </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+    </row>
+    <row r="43" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C43" s="2"/>
       <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-    </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+    </row>
+    <row r="44" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C44" s="2"/>
       <c r="D44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-    </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+    </row>
+    <row r="45" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C45" s="2"/>
       <c r="D45" s="2"/>
       <c r="E45" s="2"/>
       <c r="F45" s="2"/>
-    </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+    </row>
+    <row r="46" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C46" s="2"/>
       <c r="D46" s="2"/>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
-    </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+    </row>
+    <row r="47" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C47" s="2"/>
       <c r="D47" s="2"/>
       <c r="E47" s="2"/>
       <c r="F47" s="2"/>
-    </row>
-    <row r="48" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-    </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="4:6">
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1"/>
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:11">
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+    </row>
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+    </row>
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+    </row>
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D54" s="2"/>
+      <c r="E54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+    </row>
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+    </row>
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+    </row>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+    </row>
+    <row r="60" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C60" s="2"/>
+      <c r="D60" s="2"/>
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+    </row>
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G5 K3:L5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3 G3 F4:F5 G4:G5 H3:H5 L3:L5 C3:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="80">
   <si>
     <t>_Id</t>
   </si>
@@ -204,43 +204,73 @@
     <t>Single</t>
   </si>
   <si>
-    <t>削减敌人{0}%的护甲，最高{2}层</t>
+    <t>削减敌人{0}%的护甲，持续{1}秒，最高{2}层</t>
   </si>
   <si>
     <t>禁疗</t>
   </si>
   <si>
-    <t>降低敌人治疗效果{0}%</t>
+    <t>降低敌人治疗效果{0}%，持续{1}秒，最高{2}层</t>
   </si>
   <si>
     <t>减少敌人攻击速度</t>
   </si>
   <si>
-    <t>降低敌人{0}%的攻击速度</t>
+    <t>降低敌人{0}%的攻击速度，持续{1}秒，最高{2}层</t>
   </si>
   <si>
     <t>给敌人附加易伤</t>
   </si>
   <si>
-    <t>使敌人额外承伤{0}%，最高{2}层</t>
+    <t>使敌人额外承伤{0}%，持续{1}秒，最高{2}层</t>
   </si>
   <si>
     <t>给自己附加增伤</t>
   </si>
   <si>
-    <t>使自己额外增伤{0}%，最高{2}层</t>
-  </si>
-  <si>
-    <t>增加自己固定护甲</t>
-  </si>
-  <si>
-    <t>增加自己{1}的护甲倍率</t>
-  </si>
-  <si>
-    <t>给自己免伤</t>
-  </si>
-  <si>
-    <t>增加自己{1}的免伤倍率</t>
+    <t>使自己额外增伤{0}%，持续{1}秒，最高{2}层</t>
+  </si>
+  <si>
+    <t>增加生命倍率</t>
+  </si>
+  <si>
+    <t>增加自己{0}%的生命倍率，持续{1}秒，最高{2}层</t>
+  </si>
+  <si>
+    <t>增加防御倍率</t>
+  </si>
+  <si>
+    <t>增加自己{0}%的防御倍率，持续{1}秒，最高{2}层</t>
+  </si>
+  <si>
+    <t>增加攻击倍率</t>
+  </si>
+  <si>
+    <t>增加自己{0}%的攻击倍率，持续{1}秒，最高{2}层</t>
+  </si>
+  <si>
+    <t>增加物攻倍率</t>
+  </si>
+  <si>
+    <t>增加自己{0}%的物攻倍率，持续{1}秒，最高{2}层</t>
+  </si>
+  <si>
+    <t>增加魔攻倍率</t>
+  </si>
+  <si>
+    <t>增加自己{0}%的魔攻倍率，持续{1}秒，最高{2}层</t>
+  </si>
+  <si>
+    <t>增加道攻倍率</t>
+  </si>
+  <si>
+    <t>增加自己{0}%的道攻倍率，持续{1}秒，最高{2}层</t>
+  </si>
+  <si>
+    <t>增加增伤倍率</t>
+  </si>
+  <si>
+    <t>增加免伤倍率</t>
   </si>
   <si>
     <t>攻击回复-按物攻</t>
@@ -291,37 +321,37 @@
     <t>Interval</t>
   </si>
   <si>
-    <t>持续造成物攻{0}%的额外伤害</t>
+    <t>持续造成物攻{0}%的额外伤害，持续{1}秒，最高{2}层</t>
   </si>
   <si>
     <t>持续伤害-按法攻</t>
   </si>
   <si>
-    <t>持续造成魔攻{0}%的额外伤害</t>
+    <t>持续造成魔攻{0}%的额外伤害，持续{1}秒，最高{2}层</t>
   </si>
   <si>
     <t>持续伤害-按道攻</t>
   </si>
   <si>
-    <t>持续造成道攻{0}%的额外伤害</t>
+    <t>持续造成道攻{0}%的额外伤害，持续{1}秒，最高{2}层</t>
   </si>
   <si>
     <t>持续伤害-按防御</t>
   </si>
   <si>
-    <t>持续造成护甲{0}%的额外伤害</t>
+    <t>持续造成护甲{0}%的额外伤害，持续{1}秒，最高{2}层</t>
   </si>
   <si>
     <t>持续伤害-按生命</t>
   </si>
   <si>
-    <t>持续造成最大生命{0}%的额外伤害</t>
+    <t>持续造成最大生命{0}%的额外伤害，持续{1}秒，最高{2}层</t>
   </si>
   <si>
     <t>持续伤害-按伤害</t>
   </si>
   <si>
-    <t>持续造成技能额外伤害{0}%的额外伤害</t>
+    <t>持续造成技能额外伤害{0}%的额外伤害，持续{1}秒，最高{2}层</t>
   </si>
   <si>
     <t>麻痹</t>
@@ -524,12 +554,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1317,7 +1347,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:L61"/>
+  <dimension ref="C1:L75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
@@ -1580,242 +1610,73 @@
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C11" s="1">
-        <v>8</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="1">
-        <v>1</v>
-      </c>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1">
-        <v>1</v>
-      </c>
-      <c r="K11" s="1">
-        <v>10002</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+      <c r="L11" s="2"/>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C12" s="1">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="1">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1">
-        <v>1</v>
-      </c>
-      <c r="K12" s="1">
-        <v>10028</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="L12" s="2"/>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+      <c r="L13" s="2"/>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="D14" s="2"/>
       <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="L14" s="2"/>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="L15" s="2"/>
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C16" s="1">
-        <v>101</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="1">
-        <v>2</v>
-      </c>
-      <c r="I16" s="1">
-        <v>4</v>
-      </c>
-      <c r="J16" s="1">
-        <v>1</v>
-      </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="E16" s="2"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+      <c r="L16" s="2"/>
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C17" s="1">
-        <v>102</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H17" s="1">
-        <v>2</v>
-      </c>
-      <c r="I17" s="1">
-        <v>5</v>
-      </c>
-      <c r="J17" s="1">
-        <v>1</v>
-      </c>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+      <c r="L17" s="2"/>
     </row>
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C18" s="1">
-        <v>103</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H18" s="1">
-        <v>2</v>
-      </c>
-      <c r="I18" s="1">
-        <v>6</v>
-      </c>
-      <c r="J18" s="1">
-        <v>1</v>
-      </c>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="L18" s="2"/>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C19" s="1">
-        <v>104</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H19" s="1">
-        <v>2</v>
-      </c>
-      <c r="I19" s="1">
-        <v>2</v>
-      </c>
-      <c r="J19" s="1">
-        <v>1</v>
-      </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="E19" s="2"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+      <c r="L19" s="2"/>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C20" s="1">
-        <v>105</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H20" s="1">
-        <v>2</v>
-      </c>
-      <c r="I20" s="1">
-        <v>1</v>
-      </c>
-      <c r="J20" s="1">
-        <v>1</v>
-      </c>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C21" s="1">
-        <v>106</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>50</v>
+        <v>11</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>24</v>
@@ -1824,502 +1685,801 @@
         <v>25</v>
       </c>
       <c r="H21" s="1">
-        <v>2</v>
-      </c>
-      <c r="I21" s="1">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="I21" s="1"/>
       <c r="J21" s="1">
         <v>1</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>51</v>
+      <c r="K21" s="1">
+        <v>10001</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:12">
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
+      <c r="C22" s="1">
+        <v>12</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1">
+        <v>1</v>
+      </c>
+      <c r="K22" s="1">
+        <v>10002</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C23" s="1">
-        <v>201</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>52</v>
+        <v>13</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="E23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1</v>
+      </c>
+      <c r="K23" s="1">
+        <v>10003</v>
+      </c>
+      <c r="L23" s="2" t="s">
         <v>40</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H23" s="1">
-        <v>5</v>
-      </c>
-      <c r="I23" s="1">
-        <v>4</v>
-      </c>
-      <c r="J23" s="1">
-        <v>2</v>
-      </c>
-      <c r="K23" s="1">
-        <v>-1</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C24" s="1">
-        <v>202</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>56</v>
+        <v>14</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
+      <c r="J24" s="1">
+        <v>1</v>
+      </c>
+      <c r="K24" s="1">
+        <v>10004</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C25" s="1">
+        <v>15</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
+      <c r="J25" s="1">
+        <v>1</v>
+      </c>
+      <c r="K25" s="1">
+        <v>10005</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C26" s="1">
+        <v>16</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
+      <c r="J26" s="1">
+        <v>1</v>
+      </c>
+      <c r="K26" s="1">
+        <v>10006</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C27" s="1">
+        <v>17</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
+      <c r="J27" s="1">
+        <v>1</v>
+      </c>
+      <c r="K27" s="1">
+        <v>10027</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C28" s="1">
+        <v>18</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
+      <c r="J28" s="1">
+        <v>1</v>
+      </c>
+      <c r="K28" s="1">
+        <v>10028</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+    </row>
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C30" s="1">
+        <v>101</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H30" s="1">
+        <v>2</v>
+      </c>
+      <c r="I30" s="1">
+        <v>4</v>
+      </c>
+      <c r="J30" s="1">
+        <v>1</v>
+      </c>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C31" s="1">
+        <v>102</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H31" s="1">
+        <v>2</v>
+      </c>
+      <c r="I31" s="1">
+        <v>5</v>
+      </c>
+      <c r="J31" s="1">
+        <v>1</v>
+      </c>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G24" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H24" s="1">
-        <v>5</v>
-      </c>
-      <c r="I24" s="1">
-        <v>5</v>
-      </c>
-      <c r="J24" s="1">
-        <v>2</v>
-      </c>
-      <c r="K24" s="1">
-        <v>-1</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:12">
-      <c r="C25" s="1">
-        <v>203</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H25" s="1">
-        <v>5</v>
-      </c>
-      <c r="I25" s="1">
-        <v>6</v>
-      </c>
-      <c r="J25" s="1">
-        <v>2</v>
-      </c>
-      <c r="K25" s="1">
-        <v>-1</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:12">
-      <c r="C26" s="1">
-        <v>204</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H26" s="1">
-        <v>5</v>
-      </c>
-      <c r="I26" s="1">
-        <v>2</v>
-      </c>
-      <c r="J26" s="1">
-        <v>2</v>
-      </c>
-      <c r="K26" s="1">
-        <v>-1</v>
-      </c>
-      <c r="L26" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:12">
-      <c r="C27" s="1">
-        <v>205</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H27" s="1">
-        <v>5</v>
-      </c>
-      <c r="I27" s="1">
-        <v>1</v>
-      </c>
-      <c r="J27" s="1">
-        <v>2</v>
-      </c>
-      <c r="K27" s="1">
-        <v>-1</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:12">
-      <c r="C28" s="1">
-        <v>206</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="H28" s="1">
-        <v>5</v>
-      </c>
-      <c r="I28" s="1">
-        <v>0</v>
-      </c>
-      <c r="J28" s="1">
-        <v>2</v>
-      </c>
-      <c r="K28" s="1">
-        <v>-1</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:12">
-      <c r="C29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-    </row>
-    <row r="30" customHeight="1" spans="3:12">
-      <c r="C30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" customHeight="1" spans="3:12">
-      <c r="C31" s="1">
-        <v>901</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H31" s="1">
-        <v>3</v>
-      </c>
-      <c r="I31" s="1"/>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C32" s="1">
-        <v>902</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>25</v>
+      </c>
       <c r="H32" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:12">
+        <v>2</v>
+      </c>
+      <c r="I32" s="1">
+        <v>6</v>
+      </c>
+      <c r="J32" s="1">
+        <v>1</v>
+      </c>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="C33" s="1">
-        <v>1001</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>68</v>
+        <v>104</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="H33" s="1">
-        <v>1001</v>
-      </c>
-      <c r="L33" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="34" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C34" s="1"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-    </row>
-    <row r="35" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C35" s="1"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-    </row>
-    <row r="36" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C36" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="I33" s="1">
+        <v>2</v>
+      </c>
+      <c r="J33" s="1">
+        <v>1</v>
+      </c>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C34" s="1">
+        <v>105</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H34" s="1">
+        <v>2</v>
+      </c>
+      <c r="I34" s="1">
+        <v>1</v>
+      </c>
+      <c r="J34" s="1">
+        <v>1</v>
+      </c>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C35" s="1">
+        <v>106</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H35" s="1">
+        <v>2</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-    </row>
-    <row r="37" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-    </row>
-    <row r="38" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2"/>
-      <c r="L39" s="2"/>
-    </row>
-    <row r="40" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2"/>
-      <c r="L40" s="2"/>
-    </row>
-    <row r="41" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2"/>
-      <c r="L41" s="2"/>
-    </row>
-    <row r="42" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
-    </row>
-    <row r="43" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-    </row>
-    <row r="44" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
-    </row>
-    <row r="45" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-    </row>
-    <row r="46" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C37" s="1">
+        <v>201</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H37" s="1">
+        <v>5</v>
+      </c>
+      <c r="I37" s="1">
+        <v>4</v>
+      </c>
+      <c r="J37" s="1">
+        <v>2</v>
+      </c>
+      <c r="K37" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C38" s="1">
+        <v>202</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H38" s="1">
+        <v>5</v>
+      </c>
+      <c r="I38" s="1">
+        <v>5</v>
+      </c>
+      <c r="J38" s="1">
+        <v>2</v>
+      </c>
+      <c r="K38" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:12">
+      <c r="C39" s="1">
+        <v>203</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H39" s="1">
+        <v>5</v>
+      </c>
+      <c r="I39" s="1">
+        <v>6</v>
+      </c>
+      <c r="J39" s="1">
+        <v>2</v>
+      </c>
+      <c r="K39" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:12">
+      <c r="C40" s="1">
+        <v>204</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H40" s="1">
+        <v>5</v>
+      </c>
+      <c r="I40" s="1">
+        <v>2</v>
+      </c>
+      <c r="J40" s="1">
+        <v>2</v>
+      </c>
+      <c r="K40" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:12">
+      <c r="C41" s="1">
+        <v>205</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H41" s="1">
+        <v>5</v>
+      </c>
+      <c r="I41" s="1">
+        <v>1</v>
+      </c>
+      <c r="J41" s="1">
+        <v>2</v>
+      </c>
+      <c r="K41" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:12">
+      <c r="C42" s="1">
+        <v>206</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H42" s="1">
+        <v>5</v>
+      </c>
+      <c r="I42" s="1">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1">
+        <v>2</v>
+      </c>
+      <c r="K42" s="1">
+        <v>-1</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:12">
+      <c r="C43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+    </row>
+    <row r="44" customHeight="1" spans="3:12">
+      <c r="C44" s="1"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+    </row>
+    <row r="45" customHeight="1" spans="3:12">
+      <c r="C45" s="1">
+        <v>901</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H45" s="1">
+        <v>3</v>
+      </c>
+      <c r="I45" s="1"/>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C46" s="1">
+        <v>902</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>77</v>
+      </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-    </row>
-    <row r="47" customFormat="1" customHeight="1" spans="3:12">
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-      <c r="L47" s="2"/>
-    </row>
-    <row r="48" s="1" customFormat="1" customHeight="1"/>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="H46" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="3:12">
+      <c r="C47" s="1">
+        <v>1001</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H47" s="1">
+        <v>1001</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C48" s="1"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C49" s="1"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
-    </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C50" s="1"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
-    </row>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
       <c r="G51" s="2"/>
-    </row>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
-    </row>
-    <row r="53" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+    </row>
+    <row r="53" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
-    </row>
-    <row r="54" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+    </row>
+    <row r="54" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
-    </row>
-    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+    </row>
+    <row r="55" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
-    </row>
-    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+    </row>
+    <row r="56" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
-    </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+    </row>
+    <row r="57" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
-    </row>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+    </row>
+    <row r="58" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
-    </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+    </row>
+    <row r="59" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
       <c r="F59" s="2"/>
       <c r="G59" s="2"/>
-    </row>
-    <row r="60" customFormat="1" customHeight="1" spans="3:11">
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+    </row>
+    <row r="60" customFormat="1" customHeight="1" spans="3:12">
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
@@ -2329,16 +2489,107 @@
       <c r="I60" s="2"/>
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
-    </row>
-    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L60" s="2"/>
+    </row>
+    <row r="61" customFormat="1" customHeight="1" spans="3:12">
+      <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+    </row>
+    <row r="62" s="1" customFormat="1" customHeight="1"/>
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+    </row>
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="2"/>
+    </row>
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="2"/>
+    </row>
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="2"/>
+    </row>
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+    </row>
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="2"/>
+    </row>
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D69" s="2"/>
+      <c r="E69" s="2"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="2"/>
+    </row>
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="2"/>
+    </row>
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+    </row>
+    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
+    </row>
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="2"/>
+    </row>
+    <row r="74" customFormat="1" customHeight="1" spans="3:11">
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+    </row>
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="F3 G3 F4:F5 G4:G5 H3:H5 L3:L5 C3:E5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:H5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -71,7 +71,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -94,7 +94,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J3" authorId="1">
+    <comment ref="K3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="81">
   <si>
     <t>_Id</t>
   </si>
@@ -144,6 +144,9 @@
     <t>类型</t>
   </si>
   <si>
+    <t>SrcType</t>
+  </si>
+  <si>
     <t>来源属性</t>
   </si>
   <si>
@@ -273,7 +276,7 @@
     <t>增加免伤倍率</t>
   </si>
   <si>
-    <t>攻击回复-按物攻</t>
+    <t>攻击回复-按攻击者物攻</t>
   </si>
   <si>
     <t>After</t>
@@ -282,37 +285,37 @@
     <t>回复物攻{0}%的血量</t>
   </si>
   <si>
-    <t>攻击回复-按法攻</t>
+    <t>攻击回复-按攻击者法攻</t>
   </si>
   <si>
     <t>回复魔攻{0}%的血量</t>
   </si>
   <si>
-    <t>攻击回复-按道攻</t>
+    <t>攻击回复-按攻击者道攻</t>
   </si>
   <si>
     <t>回复道攻{0}%的血量</t>
   </si>
   <si>
-    <t>攻击回复-按防御</t>
+    <t>攻击回复-按攻击者防御</t>
   </si>
   <si>
     <t>回复护甲{0}%的血量</t>
   </si>
   <si>
-    <t>攻击回复-按生命</t>
+    <t>攻击回复-按攻击者生命</t>
   </si>
   <si>
     <t>回复最大生命{0}%的血量</t>
   </si>
   <si>
-    <t>攻击回复-按伤害</t>
+    <t>攻击回复-按攻击者伤害</t>
   </si>
   <si>
     <t>回复技能伤害{0}%的血量</t>
   </si>
   <si>
-    <t>持续伤害-按物攻</t>
+    <t>对敌人持续伤害-按攻击者物攻</t>
   </si>
   <si>
     <t>Delay</t>
@@ -324,31 +327,31 @@
     <t>持续造成物攻{0}%的额外伤害，持续{1}秒，最高{2}层</t>
   </si>
   <si>
-    <t>持续伤害-按法攻</t>
+    <t>对敌人持续伤害-按攻击者法攻</t>
   </si>
   <si>
     <t>持续造成魔攻{0}%的额外伤害，持续{1}秒，最高{2}层</t>
   </si>
   <si>
-    <t>持续伤害-按道攻</t>
+    <t>对敌人持续伤害-按攻击者道攻</t>
   </si>
   <si>
     <t>持续造成道攻{0}%的额外伤害，持续{1}秒，最高{2}层</t>
   </si>
   <si>
-    <t>持续伤害-按防御</t>
+    <t>对敌人持续伤害-按攻击者防御</t>
   </si>
   <si>
     <t>持续造成护甲{0}%的额外伤害，持续{1}秒，最高{2}层</t>
   </si>
   <si>
-    <t>持续伤害-按生命</t>
+    <t>对敌人持续伤害-按攻击者生命</t>
   </si>
   <si>
     <t>持续造成最大生命{0}%的额外伤害，持续{1}秒，最高{2}层</t>
   </si>
   <si>
-    <t>持续伤害-按伤害</t>
+    <t>对敌人持续伤害-按攻击者伤害</t>
   </si>
   <si>
     <t>持续造成技能额外伤害{0}%的额外伤害，持续{1}秒，最高{2}层</t>
@@ -1347,24 +1350,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:L75"/>
+  <dimension ref="C1:M75"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
-    <col min="4" max="7" width="17.25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.75" style="2" customWidth="1"/>
-    <col min="9" max="9" width="10.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="10" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.25" style="2" customWidth="1"/>
-    <col min="12" max="12" width="53" style="2" customWidth="1"/>
-    <col min="13" max="16381" width="9" style="2"/>
-    <col min="16383" max="16384" width="9" style="2"/>
+    <col min="4" max="4" width="26.0833333333333" style="2" customWidth="1"/>
+    <col min="5" max="7" width="17.25" style="2" customWidth="1"/>
+    <col min="8" max="9" width="9.75" style="2" customWidth="1"/>
+    <col min="10" max="10" width="10.5" style="2" customWidth="1"/>
+    <col min="11" max="11" width="10" style="2" customWidth="1"/>
+    <col min="12" max="12" width="10.25" style="2" customWidth="1"/>
+    <col min="13" max="13" width="53" style="2" customWidth="1"/>
+    <col min="14" max="16382" width="9" style="2"/>
+    <col min="16384" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="3:12">
-      <c r="I1" s="3"/>
-    </row>
-    <row r="3" customHeight="1" spans="3:12">
+    <row r="1" customHeight="1" spans="3:13">
+      <c r="J1" s="3"/>
+    </row>
+    <row r="3" customHeight="1" spans="3:13">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1395,28 +1399,31 @@
       <c r="L3" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="3:12">
+      <c r="M3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="3:13">
       <c r="C4" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>17</v>
@@ -1427,622 +1434,679 @@
       <c r="L4" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" customHeight="1" spans="3:12">
+      <c r="M4" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="3:13">
       <c r="C5" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>20</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M5" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
       </c>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1">
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1">
         <v>2</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>-10002</v>
       </c>
-      <c r="L6" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M6" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
       </c>
-      <c r="J7" s="1">
+      <c r="I7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
         <v>2</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>-10028</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M7" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C8" s="1">
         <v>4</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
       </c>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1">
+      <c r="I8" s="1">
+        <v>1</v>
+      </c>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1">
         <v>2</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>11</v>
       </c>
-      <c r="L8" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M8" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C9" s="1">
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H9" s="1">
         <v>1</v>
       </c>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1">
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1">
         <v>2</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>-10029</v>
       </c>
-      <c r="L9" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M9" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C10" s="1">
         <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
       </c>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1">
-        <v>1</v>
-      </c>
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1"/>
       <c r="K10" s="1">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1">
         <v>10027</v>
       </c>
-      <c r="L10" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M10" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E11" s="2"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M11" s="2"/>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E12" s="2"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
-      <c r="L12" s="2"/>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M12" s="2"/>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E13" s="2"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
-      <c r="L13" s="2"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M13" s="2"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E14" s="2"/>
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
-      <c r="L14" s="2"/>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M14" s="2"/>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E15" s="2"/>
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
-      <c r="L15" s="2"/>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M15" s="2"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E16" s="2"/>
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
-      <c r="L16" s="2"/>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M16" s="2"/>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E17" s="2"/>
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
-      <c r="L17" s="2"/>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M17" s="2"/>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E18" s="2"/>
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
-      <c r="L18" s="2"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M18" s="2"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E19" s="2"/>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M19" s="2"/>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E20" s="2"/>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C21" s="1">
         <v>11</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H21" s="1">
         <v>1</v>
       </c>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1">
-        <v>1</v>
-      </c>
+      <c r="I21" s="1">
+        <v>1</v>
+      </c>
+      <c r="J21" s="1"/>
       <c r="K21" s="1">
+        <v>1</v>
+      </c>
+      <c r="L21" s="1">
         <v>10001</v>
       </c>
-      <c r="L21" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M21" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C22" s="1">
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H22" s="1">
         <v>1</v>
       </c>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1">
-        <v>1</v>
-      </c>
+      <c r="I22" s="1">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1"/>
       <c r="K22" s="1">
+        <v>1</v>
+      </c>
+      <c r="L22" s="1">
         <v>10002</v>
       </c>
-      <c r="L22" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M22" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C23" s="1">
         <v>13</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H23" s="1">
         <v>1</v>
       </c>
-      <c r="J23" s="1">
+      <c r="I23" s="1">
         <v>1</v>
       </c>
       <c r="K23" s="1">
+        <v>1</v>
+      </c>
+      <c r="L23" s="1">
         <v>10003</v>
       </c>
-      <c r="L23" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M23" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C24" s="1">
         <v>14</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H24" s="1">
         <v>1</v>
       </c>
-      <c r="J24" s="1">
+      <c r="I24" s="1">
         <v>1</v>
       </c>
       <c r="K24" s="1">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1">
         <v>10004</v>
       </c>
-      <c r="L24" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M24" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C25" s="1">
         <v>15</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H25" s="1">
         <v>1</v>
       </c>
-      <c r="J25" s="1">
+      <c r="I25" s="1">
         <v>1</v>
       </c>
       <c r="K25" s="1">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1">
         <v>10005</v>
       </c>
-      <c r="L25" s="2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M25" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C26" s="1">
         <v>16</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H26" s="1">
         <v>1</v>
       </c>
-      <c r="J26" s="1">
+      <c r="I26" s="1">
         <v>1</v>
       </c>
       <c r="K26" s="1">
+        <v>1</v>
+      </c>
+      <c r="L26" s="1">
         <v>10006</v>
       </c>
-      <c r="L26" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M26" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C27" s="1">
         <v>17</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
+      <c r="I27" s="1">
+        <v>1</v>
+      </c>
+      <c r="K27" s="1">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1">
+        <v>10027</v>
+      </c>
+      <c r="M27" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H27" s="1">
-        <v>1</v>
-      </c>
-      <c r="J27" s="1">
-        <v>1</v>
-      </c>
-      <c r="K27" s="1">
-        <v>10027</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:12">
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C28" s="1">
         <v>18</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H28" s="1">
         <v>1</v>
       </c>
-      <c r="J28" s="1">
+      <c r="I28" s="1">
         <v>1</v>
       </c>
       <c r="K28" s="1">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1">
         <v>10028</v>
       </c>
-      <c r="L28" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M28" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C30" s="1">
         <v>101</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H30" s="1">
         <v>2</v>
       </c>
       <c r="I30" s="1">
+        <v>1</v>
+      </c>
+      <c r="J30" s="1">
         <v>4</v>
       </c>
-      <c r="J30" s="1">
-        <v>1</v>
-      </c>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K30" s="1">
+        <v>1</v>
+      </c>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C31" s="1">
         <v>102</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H31" s="1">
         <v>2</v>
       </c>
       <c r="I31" s="1">
+        <v>1</v>
+      </c>
+      <c r="J31" s="1">
         <v>5</v>
       </c>
-      <c r="J31" s="1">
-        <v>1</v>
-      </c>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K31" s="1">
+        <v>1</v>
+      </c>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C32" s="1">
         <v>103</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H32" s="1">
         <v>2</v>
       </c>
       <c r="I32" s="1">
+        <v>1</v>
+      </c>
+      <c r="J32" s="1">
         <v>6</v>
       </c>
-      <c r="J32" s="1">
-        <v>1</v>
-      </c>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K32" s="1">
+        <v>1</v>
+      </c>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C33" s="1">
         <v>104</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H33" s="1">
         <v>2</v>
       </c>
       <c r="I33" s="1">
+        <v>1</v>
+      </c>
+      <c r="J33" s="1">
         <v>2</v>
       </c>
-      <c r="J33" s="1">
-        <v>1</v>
-      </c>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K33" s="1">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C34" s="1">
         <v>105</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H34" s="1">
         <v>2</v>
@@ -2053,189 +2117,207 @@
       <c r="J34" s="1">
         <v>1</v>
       </c>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K34" s="1">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C35" s="1">
         <v>106</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H35" s="1">
         <v>2</v>
       </c>
       <c r="I35" s="1">
+        <v>1</v>
+      </c>
+      <c r="J35" s="1">
         <v>0</v>
       </c>
-      <c r="J35" s="1">
-        <v>1</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="K35" s="1">
+        <v>1</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="D36" s="2"/>
       <c r="E36" s="2"/>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
     </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C37" s="1">
         <v>201</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H37" s="1">
         <v>5</v>
       </c>
       <c r="I37" s="1">
+        <v>1</v>
+      </c>
+      <c r="J37" s="1">
         <v>4</v>
       </c>
-      <c r="J37" s="1">
+      <c r="K37" s="1">
         <v>2</v>
       </c>
-      <c r="K37" s="1">
+      <c r="L37" s="1">
         <v>-1</v>
       </c>
-      <c r="L37" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M37" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C38" s="1">
         <v>202</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H38" s="1">
         <v>5</v>
       </c>
       <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="1">
         <v>5</v>
       </c>
-      <c r="J38" s="1">
+      <c r="K38" s="1">
         <v>2</v>
       </c>
-      <c r="K38" s="1">
+      <c r="L38" s="1">
         <v>-1</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:12">
+      <c r="M38" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:13">
       <c r="C39" s="1">
         <v>203</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H39" s="1">
         <v>5</v>
       </c>
       <c r="I39" s="1">
+        <v>1</v>
+      </c>
+      <c r="J39" s="1">
         <v>6</v>
       </c>
-      <c r="J39" s="1">
+      <c r="K39" s="1">
         <v>2</v>
       </c>
-      <c r="K39" s="1">
+      <c r="L39" s="1">
         <v>-1</v>
       </c>
-      <c r="L39" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:12">
+      <c r="M39" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:13">
       <c r="C40" s="1">
         <v>204</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H40" s="1">
         <v>5</v>
       </c>
       <c r="I40" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J40" s="1">
         <v>2</v>
       </c>
       <c r="K40" s="1">
+        <v>2</v>
+      </c>
+      <c r="L40" s="1">
         <v>-1</v>
       </c>
-      <c r="L40" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:12">
+      <c r="M40" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:13">
       <c r="C41" s="1">
         <v>205</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G41" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H41" s="1">
         <v>5</v>
@@ -2244,75 +2326,84 @@
         <v>1</v>
       </c>
       <c r="J41" s="1">
+        <v>1</v>
+      </c>
+      <c r="K41" s="1">
         <v>2</v>
       </c>
-      <c r="K41" s="1">
+      <c r="L41" s="1">
         <v>-1</v>
       </c>
-      <c r="L41" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:12">
+      <c r="M41" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:13">
       <c r="C42" s="1">
         <v>206</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G42" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H42" s="1">
         <v>5</v>
       </c>
       <c r="I42" s="1">
+        <v>1</v>
+      </c>
+      <c r="J42" s="1">
         <v>0</v>
       </c>
-      <c r="J42" s="1">
+      <c r="K42" s="1">
         <v>2</v>
       </c>
-      <c r="K42" s="1">
+      <c r="L42" s="1">
         <v>-1</v>
       </c>
-      <c r="L42" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:12">
+      <c r="M42" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="3:13">
       <c r="C43" s="1"/>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
-    </row>
-    <row r="44" customHeight="1" spans="3:12">
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" customHeight="1" spans="3:13">
       <c r="C44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
-    </row>
-    <row r="45" customHeight="1" spans="3:12">
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" customHeight="1" spans="3:13">
       <c r="C45" s="1">
         <v>901</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H45" s="1">
         <v>3</v>
       </c>
       <c r="I45" s="1"/>
-    </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:12">
+      <c r="J45" s="1"/>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="C46" s="1">
         <v>902</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
@@ -2321,21 +2412,22 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" customHeight="1" spans="3:12">
+    <row r="47" customHeight="1" spans="3:13">
       <c r="C47" s="1">
         <v>1001</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H47" s="1">
         <v>1001</v>
       </c>
-      <c r="L47" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="48" customFormat="1" customHeight="1" spans="3:12">
+      <c r="I47" s="1"/>
+      <c r="M47" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" customFormat="1" customHeight="1" spans="3:13">
       <c r="C48" s="1"/>
       <c r="D48" s="2"/>
       <c r="E48" s="2"/>
@@ -2346,8 +2438,9 @@
       <c r="J48" s="2"/>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
-    </row>
-    <row r="49" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M48" s="2"/>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="3:13">
       <c r="C49" s="1"/>
       <c r="D49" s="2"/>
       <c r="E49" s="2"/>
@@ -2358,8 +2451,9 @@
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
       <c r="L49" s="2"/>
-    </row>
-    <row r="50" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M49" s="2"/>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="3:13">
       <c r="C50" s="1"/>
       <c r="D50" s="2"/>
       <c r="E50" s="2"/>
@@ -2370,8 +2464,9 @@
       <c r="J50" s="2"/>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
-    </row>
-    <row r="51" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M50" s="2"/>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="3:13">
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
@@ -2382,8 +2477,9 @@
       <c r="J51" s="2"/>
       <c r="K51" s="2"/>
       <c r="L51" s="2"/>
-    </row>
-    <row r="52" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M51" s="2"/>
+    </row>
+    <row r="52" customFormat="1" customHeight="1" spans="3:13">
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="2"/>
@@ -2394,8 +2490,9 @@
       <c r="J52" s="2"/>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
-    </row>
-    <row r="53" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M52" s="2"/>
+    </row>
+    <row r="53" customFormat="1" customHeight="1" spans="3:13">
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="2"/>
@@ -2406,8 +2503,9 @@
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
-    </row>
-    <row r="54" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M53" s="2"/>
+    </row>
+    <row r="54" customFormat="1" customHeight="1" spans="3:13">
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="2"/>
@@ -2418,8 +2516,9 @@
       <c r="J54" s="2"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
-    </row>
-    <row r="55" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M54" s="2"/>
+    </row>
+    <row r="55" customFormat="1" customHeight="1" spans="3:13">
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="2"/>
@@ -2430,8 +2529,9 @@
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
-    </row>
-    <row r="56" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M55" s="2"/>
+    </row>
+    <row r="56" customFormat="1" customHeight="1" spans="3:13">
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="2"/>
@@ -2442,8 +2542,9 @@
       <c r="J56" s="2"/>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
-    </row>
-    <row r="57" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M56" s="2"/>
+    </row>
+    <row r="57" customFormat="1" customHeight="1" spans="3:13">
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
@@ -2454,8 +2555,9 @@
       <c r="J57" s="2"/>
       <c r="K57" s="2"/>
       <c r="L57" s="2"/>
-    </row>
-    <row r="58" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M57" s="2"/>
+    </row>
+    <row r="58" customFormat="1" customHeight="1" spans="3:13">
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
       <c r="E58" s="2"/>
@@ -2466,8 +2568,9 @@
       <c r="J58" s="2"/>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
-    </row>
-    <row r="59" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M58" s="2"/>
+    </row>
+    <row r="59" customFormat="1" customHeight="1" spans="3:13">
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
@@ -2478,8 +2581,9 @@
       <c r="J59" s="2"/>
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
-    </row>
-    <row r="60" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M59" s="2"/>
+    </row>
+    <row r="60" customFormat="1" customHeight="1" spans="3:13">
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
@@ -2490,8 +2594,9 @@
       <c r="J60" s="2"/>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
-    </row>
-    <row r="61" customFormat="1" customHeight="1" spans="3:12">
+      <c r="M60" s="2"/>
+    </row>
+    <row r="61" customFormat="1" customHeight="1" spans="3:13">
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
@@ -2502,75 +2607,76 @@
       <c r="J61" s="2"/>
       <c r="K61" s="2"/>
       <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1"/>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="D63" s="2"/>
       <c r="E63" s="2"/>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
     </row>
-    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:12">
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="D64" s="2"/>
       <c r="E64" s="2"/>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
     </row>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D65" s="2"/>
       <c r="E65" s="2"/>
       <c r="F65" s="2"/>
       <c r="G65" s="2"/>
     </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
     </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D67" s="2"/>
       <c r="E67" s="2"/>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
     </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
     </row>
-    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
     </row>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D70" s="2"/>
       <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
     </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D71" s="2"/>
       <c r="E71" s="2"/>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
     </row>
-    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
     </row>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:11">
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
     </row>
-    <row r="74" customFormat="1" customHeight="1" spans="3:11">
+    <row r="74" customFormat="1" customHeight="1" spans="3:12">
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
@@ -2580,8 +2686,9 @@
       <c r="I74" s="2"/>
       <c r="J74" s="2"/>
       <c r="K74" s="2"/>
-    </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:11">
+      <c r="L74" s="2"/>
+    </row>
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="3:12">
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
       <c r="F75" s="2"/>
@@ -2589,7 +2696,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:H5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I3 I4 I5 M3:M5 C3:H5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="81">
   <si>
     <t>_Id</t>
   </si>
@@ -228,12 +228,6 @@
     <t>使敌人额外承伤{0}%，持续{1}秒，最高{2}层</t>
   </si>
   <si>
-    <t>给自己附加增伤</t>
-  </si>
-  <si>
-    <t>使自己额外增伤{0}%，持续{1}秒，最高{2}层</t>
-  </si>
-  <si>
     <t>增加生命倍率</t>
   </si>
   <si>
@@ -273,7 +267,13 @@
     <t>增加增伤倍率</t>
   </si>
   <si>
+    <t>增加自己{0}%的增伤倍率，持续{1}秒，最高{2}层</t>
+  </si>
+  <si>
     <t>增加免伤倍率</t>
+  </si>
+  <si>
+    <t>增加自己{0}%的免伤倍率，持续{1}秒，最高{2}层</t>
   </si>
   <si>
     <t>攻击回复-按攻击者物攻</t>
@@ -1605,37 +1605,15 @@
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:13">
-      <c r="C10" s="1">
-        <v>7</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="1">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1">
-        <v>1</v>
-      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="1">
-        <v>1</v>
-      </c>
-      <c r="L10" s="1">
-        <v>10027</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="2"/>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:13">
       <c r="E11" s="2"/>
@@ -1701,7 +1679,7 @@
         <v>11</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>24</v>
@@ -1726,7 +1704,7 @@
         <v>10001</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1734,7 +1712,7 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>24</v>
@@ -1759,7 +1737,7 @@
         <v>10002</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1767,7 +1745,7 @@
         <v>13</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>24</v>
@@ -1791,7 +1769,7 @@
         <v>10003</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1799,7 +1777,7 @@
         <v>14</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>24</v>
@@ -1823,7 +1801,7 @@
         <v>10004</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1831,7 +1809,7 @@
         <v>15</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>24</v>
@@ -1855,7 +1833,7 @@
         <v>10005</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1863,7 +1841,7 @@
         <v>16</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>24</v>
@@ -1887,7 +1865,7 @@
         <v>10006</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -1895,7 +1873,7 @@
         <v>17</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>24</v>
@@ -1927,7 +1905,7 @@
         <v>18</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>24</v>
@@ -1951,7 +1929,7 @@
         <v>10028</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:13">
@@ -2696,7 +2674,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I3 I4 I5 M3:M5 C3:H5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:M5 C3:I5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/EffectConfig.xlsx
+++ b/Excel/EffectConfig.xlsx
@@ -1532,7 +1532,7 @@
         <v>2</v>
       </c>
       <c r="L7" s="1">
-        <v>-10028</v>
+        <v>-15</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>29</v>
@@ -1598,7 +1598,7 @@
         <v>2</v>
       </c>
       <c r="L9" s="1">
-        <v>-10029</v>
+        <v>-28</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>33</v>
